--- a/v6/files/r-offer-canvas.xlsx
+++ b/v6/files/r-offer-canvas.xlsx
@@ -474,7 +474,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2. В колонке условий напишите всё, что клиент должен знать: цену после пробного периода и как отказаться. Для рекламы это требование закона.</t>
+          <t>2. В колонке условий напишите всё, что клиент должен знать: цену после пробного периода и как отказаться. Для рекламы это требование закона. Если продаёте подписку физлицам, с 1 марта 2026 года действуют новые правила автосписаний в законе о защите прав потребителей: сверьте с ними условия после пробного периода.</t>
         </is>
       </c>
     </row>
